--- a/testdata/realdata/odf.xlsx
+++ b/testdata/realdata/odf.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>容量</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,6 +464,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -481,6 +491,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +518,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -525,6 +545,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -547,6 +572,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -569,6 +599,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -591,6 +626,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -613,6 +653,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -635,6 +680,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -657,6 +707,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -679,6 +734,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -701,6 +761,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -723,6 +788,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -745,6 +815,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -765,6 +840,11 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>144</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>

--- a/testdata/realdata/odf.xlsx
+++ b/testdata/realdata/odf.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,17 +446,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ODF-279116876-01</t>
+          <t>ODF-1603990225-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>哈尔滨市01号ODF</t>
+          <t>穆棱镇01号ODF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MR279116876</t>
+          <t>MR1603990225</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -473,17 +473,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ODF-244077958-01</t>
+          <t>ODF-1727803072-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>大庆市01号ODF</t>
+          <t>讷河市01号ODF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MR244077958</t>
+          <t>MR1727803072</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -500,17 +500,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ODF-244081515-01</t>
+          <t>ODF-1933473774-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>齐齐哈尔市01号ODF</t>
+          <t>黑河市01号ODF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MR244081515</t>
+          <t>MR1933473774</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -527,17 +527,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ODF-1727803072-01</t>
+          <t>ODF-2168737545-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>讷河市01号ODF</t>
+          <t>大同区01号ODF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MR1727803072</t>
+          <t>MR2168737545</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -554,17 +554,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ODF-469656125-01</t>
+          <t>ODF-2289935762-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>嫩江市01号ODF</t>
+          <t>周家街道01号ODF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MR469656125</t>
+          <t>MR2289935762</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -581,17 +581,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ODF-678337697-01</t>
+          <t>ODF-244076868-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>加格达奇区01号ODF</t>
+          <t>巴彦县01号ODF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MR678337697</t>
+          <t>MR244076868</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ODF-962010355-01</t>
+          <t>ODF-244076933-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>塔河县01号ODF</t>
+          <t>宾县01号ODF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MR962010355</t>
+          <t>MR244076933</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -635,17 +635,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ODF-280162986-01</t>
+          <t>ODF-244077958-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>漠河市01号ODF</t>
+          <t>大庆市01号ODF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MR280162986</t>
+          <t>MR244077958</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -662,17 +662,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ODF-4059698545-01</t>
+          <t>ODF-244079035-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>牡丹江市01号ODF</t>
+          <t>方正县01号ODF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MR4059698545</t>
+          <t>MR244079035</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -689,17 +689,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ODF-304758391-01</t>
+          <t>ODF-244079624-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>佳木斯市01号ODF</t>
+          <t>甘南县01号ODF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MR304758391</t>
+          <t>MR244079624</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -716,17 +716,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ODF-6359892789-01</t>
+          <t>ODF-244080476-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>尚志市01号ODF</t>
+          <t>鹤岗市01号ODF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MR6359892789</t>
+          <t>MR244080476</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ODF-244081815-01</t>
+          <t>ODF-244080682-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>绥化市01号ODF</t>
+          <t>呼兰区01号ODF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MR244081815</t>
+          <t>MR244080682</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -770,17 +770,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ODF-244082251-01</t>
+          <t>ODF-244080693-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>伊春市01号ODF</t>
+          <t>桦南县01号ODF</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MR244082251</t>
+          <t>MR244080693</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -797,17 +797,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ODF-244081526-01</t>
+          <t>ODF-244081168-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>七台河市01号ODF</t>
+          <t>林口县01号ODF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MR244081526</t>
+          <t>MR244081168</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -824,25 +824,1861 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ODF-244081218-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>漠河市01号ODF</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MR244081218</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ODF-244081226-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>木兰县01号ODF</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MR244081226</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ODF-244081487-01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>青冈县01号ODF</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MR244081487</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ODF-244081508-01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>庆安县01号ODF</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MR244081508</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ODF-244081515-01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>齐齐哈尔市01号ODF</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MR244081515</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ODF-244081526-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>七台河市01号ODF</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MR244081526</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ODF-244081804-01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>汤原县01号ODF</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MR244081804</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ODF-244081815-01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>绥化市01号ODF</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MR244081815</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ODF-244081820-01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>绥棱县01号ODF</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MR244081820</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ODF-244081838-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>塔河县01号ODF</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MR244081838</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ODF-244081998-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>望奎县01号ODF</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MR244081998</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ODF-244082051-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>通河县01号ODF</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MR244082051</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ODF-244082251-01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>伊春市01号ODF</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MR244082251</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ODF-244082264-01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>延寿县01号ODF</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MR244082264</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ODF-244082302-01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>依兰县01号ODF</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MR244082302</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ODF-244083414-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>鄂伦春自治旗01号ODF</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MR244083414</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ODF-244083759-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>城子河区01号ODF</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MR244083759</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ODF-244083846-01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>爱民区01号ODF</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MR244083846</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ODF-244084005-01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>道里区01号ODF</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MR244084005</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ODF-244084006-01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>松北区01号ODF</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MR244084006</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ODF-244084008-01</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>香坊区01号ODF</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MR244084008</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ODF-244084009-01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>南岗区01号ODF</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MR244084009</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ODF-244084010-01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>道外区01号ODF</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MR244084010</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ODF-244084021-01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>西安区01号ODF</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MR244084021</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ODF-244084024-01</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>东安区01号ODF</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MR244084024</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ODF-244084032-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>乌翠区01号ODF</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MR244084032</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ODF-244084349-01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>龙沙区01号ODF</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MR244084349</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ODF-244084365-01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>新兴区01号ODF</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MR244084365</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ODF-279116876-01</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>哈尔滨市01号ODF</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MR279116876</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ODF-280162986-01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>漠河市01号ODF</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MR280162986</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ODF-304758391-01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>佳木斯市01号ODF</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MR304758391</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ODF-3364291968-01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>富裕县01号ODF</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MR3364291968</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ODF-3373092558-01</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>安达市01号ODF</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MR3373092558</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ODF-3373116121-01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>依安县01号ODF</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MR3373116121</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ODF-3768594801-01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>铁力市01号ODF</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MR3768594801</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ODF-3826287683-01</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>巨源镇01号ODF</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MR3826287683</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ODF-3826497558-01</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>宾西镇01号ODF</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MR3826497558</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ODF-3826497583-01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>永源镇01号ODF</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MR3826497583</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ODF-4059698545-01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>牡丹江市01号ODF</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MR4059698545</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ODF-412234770-01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>阿城区01号ODF</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MR412234770</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ODF-4417654189-01</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>伊春区01号ODF</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MR4417654189</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ODF-469656125-01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>嫩江市01号ODF</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MR469656125</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>ODF-502220401-01</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>鸡西市01号ODF</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>MR502220401</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ODF-5329377920-01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>立新街道01号ODF</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MR5329377920</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ODF-5617724009-01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>双鸭山市01号ODF</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MR5617724009</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ODF-6330273967-01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>安达市01号ODF</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MR6330273967</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ODF-6331568977-01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>肇东市01号ODF</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MR6331568977</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ODF-6332406998-01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>兰西县01号ODF</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MR6332406998</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ODF-6341507561-01</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>铁锋区01号ODF</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MR6341507561</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ODF-6343642415-01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>昂昂溪区01号ODF</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MR6343642415</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ODF-6350394662-01</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>梅里斯达斡尔族区01号ODF</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MR6350394662</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ODF-6352034081-01</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>杜尔伯特蒙古族自治县 ᠳᠥᠷᠪᠡᠳ ᠮᠣᠩᠭᠣᠯ ᠥᠪᠡᠷᠲᠡᠭᠡᠨ ᠵᠠᠰᠠᠬᠤ ᠰᠢᠶᠠᠨ01号ODF</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MR6352034081</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ODF-6352421319-01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>让胡路区01号ODF</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MR6352421319</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ODF-6353763804-01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>萨尔图区01号ODF</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MR6353763804</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ODF-6355869234-01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>肇源县01号ODF</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MR6355869234</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ODF-6356225091-01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>肇州县01号ODF</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MR6356225091</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ODF-6358882012-01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>平房区01号ODF</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MR6358882012</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ODF-6359892789-01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>尚志市01号ODF</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MR6359892789</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ODF-6373436326-01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>海林市01号ODF</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MR6373436326</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ODF-6375398861-01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>阳明区01号ODF</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MR6375398861</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ODF-6375764149-01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>穆棱市01号ODF</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MR6375764149</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ODF-6376504260-01</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>麻山区01号ODF</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MR6376504260</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ODF-6377319195-01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>恒山区01号ODF</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MR6377319195</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ODF-6380056508-01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>岭东区01号ODF</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MR6380056508</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ODF-6380925564-01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>集贤县01号ODF</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MR6380925564</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ODF-6385641267-01</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>郊区01号ODF</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MR6385641267</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ODF-6395573965-01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>勃利县01号ODF</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MR6395573965</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ODF-678337697-01</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>加格达奇区01号ODF</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MR678337697</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ODF-962010355-01</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>塔河县01号ODF</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MR962010355</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>在网</t>
         </is>
